--- a/language and skills test cases.xlsx
+++ b/language and skills test cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ramva\OneDrive\Desktop\INDUSTRY CONNECT\Internship - onboarding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BBD033-31E0-4495-9D45-653FD54F03CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC0D0E2-235D-4E0C-8E1D-8DA1D2EDA808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BD1090F1-D3A2-4828-A6AC-F41C87574BEC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{BD1090F1-D3A2-4828-A6AC-F41C87574BEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Language" sheetId="1" r:id="rId1"/>
